--- a/TFT_Hideout_WBS.xlsx
+++ b/TFT_Hideout_WBS.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K141"/>
+  <dimension ref="A1:K142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8549,6 +8549,63 @@
       <c r="K141" t="inlineStr">
         <is>
           <t>pytest — 비챔피언 엔티티(traits:[]) 필터링 단위 테스트, 챔피언 수집 결과가 임계값 미만일 때 validate_champion_collection()이 예외를 던지는지, 충분할 때는 통과하는지 단위 테스트, 기존 champion_rows/전체 배치 파이프라인 회귀 테스트 통과</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>CHAT-36</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>코딩</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>챗봇RAG</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>챗봇위젯</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>HF 임베딩 의존 제거 및 챗봇 검색 텍스트 기반(pg_trgm) 전환</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-10-18 운영 장애 조사 — 패치 18.4가 10/7부터 매일 자동 감지되지만 배치 임베딩 단계에서 실패해 is_current가 18.3에 고정됨. 원인은 Hugging Face가 2026-10-07부로 무료 계정의 월간 Inference Providers 크레딧($0.10)을 폐지(hub-docs PR #2865)해 BGE-M3 호출이 전부 402 PrepaidCreditsRequired로 거절되기 때문(계정 사용량은 8월 $0.0138·9월 $0.0027로 매우 적었음, includedNanoUsd=0 확인). 챗봇 질문 임베딩도 같은 API를 써 추천 계열 4개 의도(comp/item/augment/general_strategy)가 함께 불능. PM 결정(B안): HF를 완전히 들어내고, 배치는 청크 텍스트만 적재(벡터 없음), 챗봇 검색은 Postgres pg_trgm 텍스트 유사도로 교체. 부수 발견: 실행당 500청크 임베딩 상한 때문에 18.x 패치에는 champion/item_build 문서가 아예 없었음(상한 제거로 해소), patch_transition이 단계 실패 예외를 출력하지 않아 원인 추적 불가(로그 추가).</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>CHAT-02,DATA-11</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>이번 조사 기록(진행현황.md 2026-10-18 이력), docs/verification/CHAT-36-작업결과.md</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>배치·백엔드 어디에서도 Hugging Face를 호출하지 않음(HUGGINGFACE_API_KEY 불필요), meta_document_embeddings.embedding nullable 전환 + pg_trgm 확장 설치 마이그레이션, 배치가 HF 없이 해당 패치의 전체 청크(상한 없음)를 적재하고 패치 승격까지 성공, 챗봇 4개 RAG 의도가 pg_trgm 기반 이름/본문 유사도로 검색, 기존 검색 정책(CHAT-15 item/augment 오검색 차단, CHAT-18 활성·티어 우선 정렬, CHAT-02 general_strategy doc_type 균등배분, item_build 챔피언별 균등) 유지, 배치 단계 실패 시 예외 내용이 로그로 출력됨</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>pytest — 텍스트 검색 단위 테스트(이름 정확 일치 우선, 존재하지 않는 이름 차단, 활성·티어 정렬 유지, item_build 챔피언별 상한, 구성 챔피언/아이템 이름으로 조합·빌드 검색), 배치 청크 적재가 벡터 없이 upsert되는지, comps 재수집이 HF 없이 동작하는지, 마이그레이션 upgrade/downgrade, 기존 backend/batch 전체 회귀 통과</t>
         </is>
       </c>
     </row>

--- a/TFT_Hideout_WBS.xlsx
+++ b/TFT_Hideout_WBS.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K142"/>
+  <dimension ref="A1:K147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8606,6 +8606,291 @@
       <c r="K142" t="inlineStr">
         <is>
           <t>pytest — 텍스트 검색 단위 테스트(이름 정확 일치 우선, 존재하지 않는 이름 차단, 활성·티어 정렬 유지, item_build 챔피언별 상한, 구성 챔피언/아이템 이름으로 조합·빌드 검색), 배치 청크 적재가 벡터 없이 upsert되는지, comps 재수집이 HF 없이 동작하는지, 마이그레이션 upgrade/downgrade, 기존 backend/batch 전체 회귀 통과</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>DATA-25</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>코딩</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>데이터파이프라인</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>champion_item_builds 디스크 IO 개선(인덱스·일괄 교체·지난 패치 정리)</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-10-26 Supabase가 "Disk IO Budget 고갈" 경고 메일 발송. 조사 결과 (1) CHAT-36 이전 HF 402로 패치 승격이 10/7부터 매일 실패하며 전체 재수집이 반복돼 champion_item_builds에 누적 146만 행 삽입·106만 행 삭제 (2) 이 테이블에 PK 외 인덱스가 없어 배치의 챔피언별 DELETE(실행당 약 65회)가 매번 80MB·40만 행 전체를 순차 스캔(누적 seq_tup_read 약 5.4억) (3) 17.8~18.5 지난 패치 빌드 40만 행(깨진 18.1만 13만 행)이 정리 없이 누적. CHAT-36 머지로 반복 재수집은 멈췄으나 구조 문제는 남아 다음 패치 때 재발 가능.</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>필수</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>DATA-10,DATA-13</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>진행현황.md 2026-10-26 이력, docs/verification/DATA-25-작업결과.md</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>champion_item_builds에 (patch_version, champion_id) 인덱스 추가 마이그레이션, 배치가 패치 단위 DELETE 1회 + 청크 단위 INSERT로 빌드를 교체, 배치 성공(승격) 후 최근 2개 패치를 제외한 지난 패치의 빌드 행 정리, 기존 배치·카탈로그 동작 회귀 없음</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>pytest — 패치 단위 교체가 다른 패치 행을 건드리지 않는지, 청크 경계보다 큰 입력도 전부 적재되는지, 정리 로직이 최근 2개 패치만 남기는지, 인덱스 마이그레이션 upgrade/downgrade, 기존 backend/batch 전체 회귀 통과</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>DATA-26</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>코딩</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>데이터파이프라인</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Set 18 챔피언 검색 문서(champion doc_type) 생성 복구</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>CHAT-36 실데이터 검증 중 발견 — Set 18 챔피언 ID가 DA_18_*, DA_Amumu18, DA_Lux18_Blossom 등 혼합 형식이라 embeddings.is_real_champion()(TFT{set}_ 접두어 검사)을 하나도 통과 못해 champion 검색 문서가 0건. "3코스트 챔피언은?" 같은 질문의 근거 문서가 없음. 정글 몬스터 변형(심술두꺼비·어스름늑대 등)과 동일 챔피언 변형(럭스 개화/검은 가시) 처리 기준도 함께 정해야 함.</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>권장</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>DATA-11,DATA-24</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>docs/verification/CHAT-36-작업결과.md PM 확인 사항 2</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Set 18 패치에서 실제 구매 가능한 챔피언만 champion 문서로 생성됨(비챔피언·변형 처리 기준 PM 확정), Set 17 이하 기존 동작 회귀 없음</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>pytest — Set 18 ID 형식 판별 단위 테스트, Set 17 회귀 테스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>CHAT-37</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>코딩</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>챗봇RAG</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>챗봇위젯</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>비활성 조합 이름 지목 시 검색 노출 정책 검토</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>CHAT-36 실데이터 검증 중 발견 — "달빛 세주아니 조합 어때?"처럼 op.gg 상위 10위 밖으로 밀려난(is_active=false) 조합을 이름으로 직접 물어도, CHAT-18 정책(비활성은 항상 활성 뒤)에 따라 검색 결과에 나오지 않음(벡터 검색 시절과 동일, 회귀 아님). 질의가 조합명을 직접 지목하면 비활성이어도 포함할지 PM 결정 필요(문서엔 이미 "상위 10위 밖" 주의 문구가 있어 LLM이 캐비엇을 담).</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>권장</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>CHAT-18,CHAT-36</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>docs/verification/CHAT-36-작업결과.md PM 확인 사항 1</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>PM 결정에 따라 정책 확정 — 변경 시 조합명 직접 지목 질의에서 비활성 조합이 주의 문구와 함께 검색되고, 일반 질의의 활성 우선 정렬은 유지</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>pytest — 조합명 직접 지목 시 비활성 조합 포함, 일반 질의 시 활성 우선 유지(CHAT-18 회귀)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>SET-18</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>시스템설정</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Supabase Data API(PostgREST) 미사용 설정 정리</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-10-26 조사 — Supabase Postgres 로그에 약 32초마다 schema "pg_pgrst_no_exposed_schemas" does not exist(3F000) 에러가 반복(시간당 약 112건). 노출 스키마가 비어 PostgREST가 placeholder 스키마를 로드하려다 실패하는 것으로 앱 영향 없음. 단 public 테이블 21개 전부 RLS 미적용이라 public을 다시 노출하는 해결책은 금지.</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>진행현황.md 2026-10-26 이력</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Data API 비활성화 또는 빈 전용 스키마 노출로 해당 에러 로그가 멈춤, public 스키마는 계속 미노출</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>해당 없음(인프라 설정) — Logs Explorer에서 에러 중단 확인 결과를 docs/verification/smoke-tests.md에 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>SET-19</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>시스템설정</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>GitHub Actions 액션 버전·러너 이미지 업데이트</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-10-26 배치 수동 실행 시 Annotations 경고 — actions/checkout@v4·setup-python@v5 등이 Node.js 20 대상이라 지원 종료 예정, ubuntu-latest 라벨이 2026-10-19부터 Ubuntu 26으로 이전. 당장 실패는 없으나 향후 워크플로 중단 위험.</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>권장</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>SET-14</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>진행현황.md 2026-10-26 이력</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>ci.yml·patch-detection.yml·manual-smoke.yml의 액션을 Node 24 지원 버전으로 갱신, 러너 이미지 변경 후 CI·배치 워크플로 정상 동작</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>해당 없음(CI 설정) — 갱신 후 CI·배치 워크플로 1회 실행 성공 확인</t>
         </is>
       </c>
     </row>
